--- a/Planilhas_importação/importar_fornecedor.xlsx
+++ b/Planilhas_importação/importar_fornecedor.xlsx
@@ -42,8 +42,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informar o nome completo do fornecedor, caso seja uma pessoa física, ou a razão social completa, sendo pessoa jurídica.</t>
         </r>
@@ -66,8 +66,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe a data de nascimento do fornecedor. Formato: DD/MM/YYYY ou YYYY/MM/DD.</t>
         </r>
@@ -78,8 +78,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe a nacionalidade do fornecedor (nome do país onde nasceu).</t>
         </r>
@@ -90,8 +90,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe a naturalidade do fornecedor (nome da cidade onde nasceu).</t>
         </r>
@@ -102,8 +102,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe a naturalidade do fornecedor (sigla do estado onde nasceu).
 Ex.: BA para quem nasceu no estado da Bahia.</t>
@@ -115,8 +115,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe a profissão do fornecedor.</t>
         </r>
@@ -143,8 +143,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe se o fornecedor convive em união estável: 
 - SIM 
@@ -157,8 +157,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe o nome da mãe do fornecedor.</t>
         </r>
@@ -169,8 +169,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe o nome do pai do fornecedor.</t>
         </r>
@@ -181,8 +181,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe o tipo do documento de identificação do fornecedor:
 </t>
@@ -192,6 +192,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">- RG
 - RNE
@@ -207,8 +208,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe o número do documento de identificação do fornecedor.</t>
         </r>
@@ -219,8 +220,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe o órgão emissor do documento de identificação do fornecedor.
 Ex.: SSP</t>
@@ -232,8 +233,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe o e-mail do fornecedor.</t>
         </r>
@@ -244,8 +245,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informe o tipo de telefone para contato com o fornecedor:
 </t>
@@ -255,6 +256,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">- CELULAR
 - FIXO
@@ -268,8 +270,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informar utilizando o padrão a seguir: Celular: 5573999341121 Telefone fixo: 557330130001</t>
         </r>
@@ -280,8 +282,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informar o CEP referente ao endereço do fornecedor.</t>
         </r>
@@ -292,8 +294,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informar o logradouro referente ao endereço do fornecedor.</t>
         </r>
@@ -304,8 +306,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informar o número do imóvel referente ao endereço do fornecedor.</t>
         </r>
@@ -316,8 +318,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informar o bairro referente ao endereço do fornecedor.</t>
         </r>
@@ -328,8 +330,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informar a cidade referente ao endereço do fornecedor.</t>
         </r>
@@ -340,8 +342,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informar o Estado referente ao endereço do fornecedor.
 Ex.: BA</t>
@@ -353,8 +355,8 @@
         <r>
           <rPr>
             <sz val="10"/>
-            <rFont val="Liberation Serif;Times New Roman"/>
-            <family val="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Opcional. Informar o complemento referente ao endereço do fornecedor (apartamento, 1° andar, fundos, etc.).</t>
         </r>
@@ -509,8 +511,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Liberation Serif;Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -528,7 +531,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
+        <fgColor rgb="FF34B3FB"/>
         <bgColor rgb="FF00CCFF"/>
       </patternFill>
     </fill>
@@ -569,6 +572,36 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
@@ -599,37 +632,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -671,30 +674,30 @@
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal" xfId="20"/>
-    <cellStyle name="heading 1" xfId="21"/>
-    <cellStyle name="heading 2" xfId="22"/>
-    <cellStyle name="heading 3" xfId="23"/>
-    <cellStyle name="heading 4" xfId="24"/>
-    <cellStyle name="heading 5" xfId="25"/>
-    <cellStyle name="heading 6" xfId="26"/>
+    <cellStyle name="Body Text" xfId="20"/>
+    <cellStyle name="caption" xfId="21"/>
+    <cellStyle name="Caracteres de nota de fim" xfId="22"/>
+    <cellStyle name="Caracteres de nota de rodapé" xfId="23"/>
+    <cellStyle name="Conteúdo da tabela" xfId="24"/>
+    <cellStyle name="endnote reference" xfId="25"/>
+    <cellStyle name="endnote text" xfId="26"/>
     <cellStyle name="Endnote Text Char" xfId="27"/>
-    <cellStyle name="endnote reference" xfId="28"/>
-    <cellStyle name="Caracteres de nota de fim" xfId="29"/>
+    <cellStyle name="footnote reference" xfId="28"/>
+    <cellStyle name="footnote text" xfId="29"/>
     <cellStyle name="Footnote Text Char" xfId="30"/>
-    <cellStyle name="footnote reference" xfId="31"/>
-    <cellStyle name="Caracteres de nota de rodapé" xfId="32"/>
-    <cellStyle name="endnote text" xfId="33"/>
-    <cellStyle name="footnote text" xfId="34"/>
-    <cellStyle name="List Paragraph" xfId="35"/>
-    <cellStyle name="Strong Emphasis" xfId="36"/>
-    <cellStyle name="Title" xfId="37"/>
-    <cellStyle name="Índice" xfId="38"/>
-    <cellStyle name="caption" xfId="39"/>
-    <cellStyle name="List" xfId="40"/>
-    <cellStyle name="Body Text" xfId="41"/>
+    <cellStyle name="heading 1 1" xfId="31"/>
+    <cellStyle name="heading 2 2" xfId="32"/>
+    <cellStyle name="heading 3" xfId="33"/>
+    <cellStyle name="heading 4" xfId="34"/>
+    <cellStyle name="heading 5" xfId="35"/>
+    <cellStyle name="heading 6" xfId="36"/>
+    <cellStyle name="List" xfId="37"/>
+    <cellStyle name="List Paragraph" xfId="38"/>
+    <cellStyle name="Normal" xfId="39"/>
+    <cellStyle name="Strong Emphasis" xfId="40"/>
+    <cellStyle name="Title" xfId="41"/>
     <cellStyle name="Título de tabela" xfId="42"/>
-    <cellStyle name="Conteúdo da tabela" xfId="43"/>
+    <cellStyle name="Índice" xfId="43"/>
     <cellStyle name="Destaque 3" xfId="44"/>
   </cellStyles>
   <colors>
@@ -956,7 +959,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="20.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="31.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="34.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="34.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="34.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="23"/>
